--- a/results/Int All Data -0.1/Linea_fi_all.xlsx
+++ b/results/Int All Data -0.1/Linea_fi_all.xlsx
@@ -1616,7 +1616,7 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>6.711409395971923e-05 +/- 0.0010904749536424056</t>
+          <t>0.00013422818791946066 +/- 0.001073825503355696</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -3901,7 +3901,7 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>0.015421853388658424 +/- 0.0013409902786767115</t>
+          <t>0.015352697095435741 +/- 0.0012676557939020258</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>0.0008644536652835377 +/- 0.0004441643353618632</t>
+          <t>0.0007952973720608547 +/- 0.0004387474944830386</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -4341,74 +4341,74 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>0.014183185235816798 +/- 0.0018293128764282488</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0.004750512645249472 +/- 0.0021092650887504436</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>-0.0002050580997949636 +/- 0.001252925685565515</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0.0054682159945317775 +/- 0.0010252904989746959</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>0.0028708133971291905 +/- 0.0007037341176341022</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0.01558441558441559 +/- 0.0021625826410876774</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0.010457963089542022 +/- 0.0016964693979481785</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>-0.0043062200956938135 +/- 0.0016964693979481787</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0.01565276828434724 +/- 0.0018006753072207196</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>0.0021189336978810645 +/- 0.0014321481093477154</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0.006561859193438125 +/- 0.0009881635198086768</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>0.001332877648667108 +/- 0.0011685113463621888</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>0.0037252221462747647 +/- 0.0008434014134827833</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
           <t>0.014217361585782629 +/- 0.0018353686373339124</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>0.004750512645249472 +/- 0.0021092650887504436</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>-0.0002050580997949636 +/- 0.001252925685565515</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>0.0054682159945317775 +/- 0.0010252904989746959</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>0.0028708133971291905 +/- 0.0007037341176341022</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0.01558441558441559 +/- 0.0021625826410876774</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>0.010457963089542022 +/- 0.0016964693979481785</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>-0.0043062200956938135 +/- 0.0016964693979481787</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0.01565276828434724 +/- 0.0018006753072207196</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>0.0021189336978810645 +/- 0.0014321481093477154</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>0.006561859193438125 +/- 0.0009881635198086768</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>0.001332877648667108 +/- 0.0011685113463621888</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>0.0037252221462747647 +/- 0.0008434014134827833</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>0.014183185235816798 +/- 0.0018293128764282488</t>
-        </is>
-      </c>
       <c r="W6" t="inlineStr">
         <is>
           <t>0.001913875598086112 +/- 0.0013687617494532417</t>
@@ -4736,7 +4736,7 @@
       </c>
       <c r="CJ6" t="inlineStr">
         <is>
-          <t>6.835269993162862e-05 +/- 0.0003680905541445449</t>
+          <t>0.00010252904989744848 +/- 0.000375939849624072</t>
         </is>
       </c>
       <c r="CK6" t="inlineStr">
@@ -5776,7 +5776,7 @@
       </c>
       <c r="EK7" t="inlineStr">
         <is>
-          <t>-0.004087102177554392 +/- 0.001548304188715755</t>
+          <t>-0.00412060301507533 +/- 0.001513481674784119</t>
         </is>
       </c>
       <c r="EL7" t="inlineStr">
@@ -6266,7 +6266,7 @@
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>3.218538783394953e-05 +/- 0.00022529771483745638</t>
+          <t>6.437077566787686e-05 +/- 0.00024085338826996104</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -7026,7 +7026,7 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>0.0285665058580289 +/- 0.004549239766899375</t>
+          <t>0.028600964851826283 +/- 0.004508732524823195</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
@@ -8661,7 +8661,7 @@
       </c>
       <c r="CT11" t="inlineStr">
         <is>
-          <t>0.058254799301919694 +/- 0.0047228884276765025</t>
+          <t>0.05821989528795809 +/- 0.004695335908076872</t>
         </is>
       </c>
       <c r="CU11" t="inlineStr">
